--- a/ARM Functions/Item Edits/Mega Stone Magic Guard.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Magic Guard.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67D4F3F6-9AF1-4050-B3F0-DC2DDB154BCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5FBBF3-645E-4EB6-A943-42A172EE87D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>notes</t>
   </si>
@@ -102,12 +102,6 @@
     <t>bl 0x00092298</t>
   </si>
   <si>
-    <t>ldrh r0, [r0, 0xC]</t>
-  </si>
-  <si>
-    <t>BC00D0E1</t>
-  </si>
-  <si>
     <t>0F402DE9</t>
   </si>
   <si>
@@ -129,69 +123,12 @@
     <t>mov r1, r2</t>
   </si>
   <si>
-    <t>get species</t>
-  </si>
-  <si>
-    <t>get table</t>
-  </si>
-  <si>
-    <t>0020A0E3</t>
-  </si>
-  <si>
-    <t>mov r2, 0x0</t>
-  </si>
-  <si>
-    <t>B23091E1</t>
-  </si>
-  <si>
-    <t>ldrh r3, [r1, r2]</t>
-  </si>
-  <si>
-    <t>030050E1</t>
-  </si>
-  <si>
-    <t>cmp r0, r3</t>
-  </si>
-  <si>
-    <t>000050E3</t>
-  </si>
-  <si>
-    <t>cmp r0, 0x0</t>
-  </si>
-  <si>
-    <t>022082E2</t>
-  </si>
-  <si>
-    <t>add r2, r2, 0x2</t>
-  </si>
-  <si>
     <t>0F40BDE8</t>
   </si>
   <si>
     <t>0F80BDE8</t>
   </si>
   <si>
-    <t>Table of valid Pokemon</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>28109FE5</t>
-  </si>
-  <si>
-    <t>0300000A</t>
-  </si>
-  <si>
-    <t>F8FFFFEA</t>
-  </si>
-  <si>
-    <t>Alakazam</t>
-  </si>
-  <si>
-    <t>0014AF00</t>
-  </si>
-  <si>
     <t>Mega Stone Magic Guard 0x98</t>
   </si>
   <si>
@@ -207,7 +144,22 @@
     <t>9240FEEB</t>
   </si>
   <si>
-    <t>8154FFEA</t>
+    <t>bl 0x000D6F98</t>
+  </si>
+  <si>
+    <t>cmp r1, 0x1</t>
+  </si>
+  <si>
+    <t>D153FFEB</t>
+  </si>
+  <si>
+    <t>010051E3</t>
+  </si>
+  <si>
+    <t>0100001A</t>
+  </si>
+  <si>
+    <t>8854FFEA</t>
   </si>
 </sst>
 </file>
@@ -612,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B45B0BF-76E7-4635-9005-9D6B1877FAE8}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -649,7 +601,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="3" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="str">
         <f>_xlfn.CONCAT("0",RIGHT(C3,1),"10A0E3")</f>
@@ -714,18 +666,18 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -734,25 +686,25 @@
         <v>00102040</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>18</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="str">
-        <f t="shared" ref="A12:A27" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
+        <f t="shared" ref="A12:A19" si="1">DEC2HEX(HEX2DEC(A11)+4,8)</f>
         <v>00102044</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="5"/>
     </row>
@@ -762,7 +714,7 @@
         <v>00102048</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>13</v>
@@ -775,29 +727,23 @@
         <v>0010204C</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>23</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00102050</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, #",HEX2DEC(A27)-HEX2DEC(A15)-8,"]")</f>
-        <v>ldr r1, [pc, #40]</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>24</v>
+      <c r="B15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -806,387 +752,71 @@
         <v>00102054</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="str">
+        <f>_xlfn.CONCAT("bne 0x",A19)</f>
+        <v>bne 0x00102060</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00102058</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>21</v>
+      </c>
+      <c r="C17" s="2" t="str">
+        <f>SUBSTITUTE(C10,"push","pop")</f>
+        <v>pop {r0, r1, r2, r3, lr}</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>0010205C</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>29</v>
+      <c r="B18" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>00102060</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="C19" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A24)</f>
-        <v>beq 0x00102074</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102064</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102068</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <f>_xlfn.CONCAT("beq 0x",A26)</f>
-        <v>beq 0x0010207C</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>0010206C</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102070</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <f>_xlfn.CONCAT("b 0x",A17)</f>
-        <v>b 0x00102058</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102074</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <f>SUBSTITUTE(C10,"push","pop")</f>
-        <v>pop {r0, r1, r2, r3, lr}</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102078</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>0010207C</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="2" t="str">
-        <f>SUBSTITUTE(C24,"lr","pc")</f>
+        <f>SUBSTITUTE(C17,"lr","pc")</f>
         <v>pop {r0, r1, r2, r3, pc}</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>00102080</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="2" t="str">
-        <f>RIGHT(E30,2)&amp;LEFT(E30,2)</f>
-        <v>4100</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="2">
-        <v>65</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <f>DEC2HEX(D30,4)</f>
-        <v>0041</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="2" t="str">
-        <f>DEC2HEX(HEX2DEC(A30)+2,8)</f>
-        <v>0014AF02</v>
-      </c>
-      <c r="B31" s="2" t="str">
-        <f t="shared" ref="B31:B45" si="2">RIGHT(E31,2)&amp;LEFT(E31,2)</f>
-        <v>0000</v>
-      </c>
-      <c r="C31" s="6"/>
-      <c r="E31" s="2" t="str">
-        <f t="shared" ref="E31:E45" si="3">DEC2HEX(D31,4)</f>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="2" t="str">
-        <f t="shared" ref="A32:A45" si="4">DEC2HEX(HEX2DEC(A31)+2,8)</f>
-        <v>0014AF04</v>
-      </c>
-      <c r="B32" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="C32" s="6"/>
-      <c r="E32" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF06</v>
-      </c>
-      <c r="B33" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="C33" s="6"/>
-      <c r="E33" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF08</v>
-      </c>
-      <c r="B34" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="C34" s="6"/>
-      <c r="E34" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF0A</v>
-      </c>
-      <c r="B35" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF0C</v>
-      </c>
-      <c r="B36" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF0E</v>
-      </c>
-      <c r="B37" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF10</v>
-      </c>
-      <c r="B38" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E38" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF12</v>
-      </c>
-      <c r="B39" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E39" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF14</v>
-      </c>
-      <c r="B40" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF16</v>
-      </c>
-      <c r="B41" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF18</v>
-      </c>
-      <c r="B42" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E42" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF1A</v>
-      </c>
-      <c r="B43" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E43" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF1C</v>
-      </c>
-      <c r="B44" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E44" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v>0014AF1E</v>
-      </c>
-      <c r="B45" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>0000</v>
-      </c>
-      <c r="E45" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v>0000</v>
-      </c>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="C22" s="6"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="C23" s="6"/>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="C24" s="6"/>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="C26" s="6"/>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="C27" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ARM Functions/Item Edits/Mega Stone Magic Guard.xlsx
+++ b/ARM Functions/Item Edits/Mega Stone Magic Guard.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5FBBF3-645E-4EB6-A943-42A172EE87D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
+    <workbookView xWindow="-16466" yWindow="0" windowWidth="16466" windowHeight="17914" xr2:uid="{6B563214-6527-4E5F-B5EA-E821D6DED3A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Code" sheetId="1" r:id="rId1"/>
